--- a/public/file/siswa.xlsx
+++ b/public/file/siswa.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21126"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CA785F-C534-4487-9817-AB674E038CDF}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{5928E326-D99B-43BE-A58D-23EBF218C688}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23256" windowHeight="12108"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="364">
   <si>
     <t>nis</t>
   </si>
@@ -147,9 +141,6 @@
     <t>X TITL 1</t>
   </si>
   <si>
-    <t>6285274817886</t>
-  </si>
-  <si>
     <t>Afzal Zikri</t>
   </si>
   <si>
@@ -931,12 +922,201 @@
   </si>
   <si>
     <t>XII TPTUP</t>
+  </si>
+  <si>
+    <t>6281363138584</t>
+  </si>
+  <si>
+    <t>6282169546118</t>
+  </si>
+  <si>
+    <t>6285376716907</t>
+  </si>
+  <si>
+    <t>6281275474789</t>
+  </si>
+  <si>
+    <t>6281263219176</t>
+  </si>
+  <si>
+    <t>6282392003652</t>
+  </si>
+  <si>
+    <t>6282387200905</t>
+  </si>
+  <si>
+    <t>6285767204987</t>
+  </si>
+  <si>
+    <t>6285875515489</t>
+  </si>
+  <si>
+    <t>628126719476</t>
+  </si>
+  <si>
+    <t>6283867136969</t>
+  </si>
+  <si>
+    <t>6282382224522</t>
+  </si>
+  <si>
+    <t>6289635547586</t>
+  </si>
+  <si>
+    <t>6281378136336</t>
+  </si>
+  <si>
+    <t>6281363669817</t>
+  </si>
+  <si>
+    <t>6285376764690</t>
+  </si>
+  <si>
+    <t>6282389688383</t>
+  </si>
+  <si>
+    <t>6281371880818</t>
+  </si>
+  <si>
+    <t>6281268326181</t>
+  </si>
+  <si>
+    <t>62895340127898</t>
+  </si>
+  <si>
+    <t>628896699452</t>
+  </si>
+  <si>
+    <t>6281378137777</t>
+  </si>
+  <si>
+    <t>6282171604183</t>
+  </si>
+  <si>
+    <t>6282330963059</t>
+  </si>
+  <si>
+    <t>6283146371688</t>
+  </si>
+  <si>
+    <t>6285271282691</t>
+  </si>
+  <si>
+    <t>6281363141014</t>
+  </si>
+  <si>
+    <t>6285274818939</t>
+  </si>
+  <si>
+    <t>6285376008872</t>
+  </si>
+  <si>
+    <t>6282388456606</t>
+  </si>
+  <si>
+    <t>6281378113275</t>
+  </si>
+  <si>
+    <t>6283802010004</t>
+  </si>
+  <si>
+    <t>6281287011547</t>
+  </si>
+  <si>
+    <t>6285356951733</t>
+  </si>
+  <si>
+    <t>6282389083890</t>
+  </si>
+  <si>
+    <t>6285374452056</t>
+  </si>
+  <si>
+    <t>6281266474123</t>
+  </si>
+  <si>
+    <t>6283833342086</t>
+  </si>
+  <si>
+    <t>6282284598026</t>
+  </si>
+  <si>
+    <t>6281363842152</t>
+  </si>
+  <si>
+    <t>6281266010335</t>
+  </si>
+  <si>
+    <t>6282389206021</t>
+  </si>
+  <si>
+    <t>6285356674506</t>
+  </si>
+  <si>
+    <t>6283152159287</t>
+  </si>
+  <si>
+    <t>6282385882850</t>
+  </si>
+  <si>
+    <t>6285363707772</t>
+  </si>
+  <si>
+    <t>6283159688680</t>
+  </si>
+  <si>
+    <t>6283196868716</t>
+  </si>
+  <si>
+    <t>6285271090605</t>
+  </si>
+  <si>
+    <t>6283866879168</t>
+  </si>
+  <si>
+    <t>6285272913369</t>
+  </si>
+  <si>
+    <t>6281389571115</t>
+  </si>
+  <si>
+    <t>6285263562304</t>
+  </si>
+  <si>
+    <t>6285274315087</t>
+  </si>
+  <si>
+    <t>6281267691295</t>
+  </si>
+  <si>
+    <t>6283182678051</t>
+  </si>
+  <si>
+    <t>6282170253477</t>
+  </si>
+  <si>
+    <t>6285373321586</t>
+  </si>
+  <si>
+    <t>6282297498330</t>
+  </si>
+  <si>
+    <t>6283183015295</t>
+  </si>
+  <si>
+    <t>6282387605921</t>
+  </si>
+  <si>
+    <t>6281374507200</t>
+  </si>
+  <si>
+    <t>6281364794821</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1086,9 +1266,9 @@
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{385E58EC-BD85-48CC-8114-B01CFFB8D35E}"/>
-    <cellStyle name="Normal 3" xfId="1" xr:uid="{3A8C639A-BB4B-4E01-9E5D-E963D8E847AE}"/>
-    <cellStyle name="Normal 7" xfId="3" xr:uid="{C8DE59C2-66B3-419F-93E2-6AB050879A4C}"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 3" xfId="1"/>
+    <cellStyle name="Normal 7" xfId="3"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -1157,7 +1337,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1209,7 +1389,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1403,23 +1583,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C7C71C-2511-4DCF-AEA5-18AC1E5FC3EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D291"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1433,7 +1613,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>36114</v>
       </c>
@@ -1444,10 +1624,10 @@
         <v>39</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>36115</v>
       </c>
@@ -1457,8 +1637,11 @@
       <c r="C3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D3" s="8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>36116</v>
       </c>
@@ -1468,8 +1651,11 @@
       <c r="C4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D4" s="8" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>36117</v>
       </c>
@@ -1479,8 +1665,11 @@
       <c r="C5" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D5" s="8" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>36118</v>
       </c>
@@ -1490,8 +1679,11 @@
       <c r="C6" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D6" s="8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>36119</v>
       </c>
@@ -1501,8 +1693,11 @@
       <c r="C7" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D7" s="8" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>36120</v>
       </c>
@@ -1512,8 +1707,11 @@
       <c r="C8" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D8" s="8" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>36121</v>
       </c>
@@ -1523,8 +1721,11 @@
       <c r="C9" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D9" s="8" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>36122</v>
       </c>
@@ -1534,8 +1735,11 @@
       <c r="C10" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D10" s="8" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>36123</v>
       </c>
@@ -1545,8 +1749,11 @@
       <c r="C11" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D11" s="8" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>36124</v>
       </c>
@@ -1556,8 +1763,11 @@
       <c r="C12" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D12" s="8" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>36125</v>
       </c>
@@ -1567,8 +1777,11 @@
       <c r="C13" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D13" s="8" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>36126</v>
       </c>
@@ -1578,8 +1791,11 @@
       <c r="C14" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D14" s="8" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>36127</v>
       </c>
@@ -1590,7 +1806,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>36128</v>
       </c>
@@ -1600,8 +1816,11 @@
       <c r="C16" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" s="8" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>36129</v>
       </c>
@@ -1611,8 +1830,11 @@
       <c r="C17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" s="8" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>36130</v>
       </c>
@@ -1622,8 +1844,11 @@
       <c r="C18" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" s="8" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>36131</v>
       </c>
@@ -1633,8 +1858,11 @@
       <c r="C19" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" s="8" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>36132</v>
       </c>
@@ -1644,8 +1872,11 @@
       <c r="C20" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" s="8" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>36133</v>
       </c>
@@ -1655,8 +1886,11 @@
       <c r="C21" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" s="8" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>36134</v>
       </c>
@@ -1666,8 +1900,11 @@
       <c r="C22" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" s="8" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>36135</v>
       </c>
@@ -1677,8 +1914,11 @@
       <c r="C23" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" s="8" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>36136</v>
       </c>
@@ -1688,8 +1928,11 @@
       <c r="C24" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" s="8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>36137</v>
       </c>
@@ -1699,8 +1942,11 @@
       <c r="C25" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" s="8" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>36138</v>
       </c>
@@ -1710,8 +1956,11 @@
       <c r="C26" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" s="8" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>36139</v>
       </c>
@@ -1721,8 +1970,11 @@
       <c r="C27" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" s="8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>36140</v>
       </c>
@@ -1732,8 +1984,11 @@
       <c r="C28" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" s="8" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>36141</v>
       </c>
@@ -1744,7 +1999,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>36142</v>
       </c>
@@ -1754,8 +2009,11 @@
       <c r="C30" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" s="8" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>36143</v>
       </c>
@@ -1765,8 +2023,11 @@
       <c r="C31" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" s="8" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>36144</v>
       </c>
@@ -1777,7 +2038,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>36145</v>
       </c>
@@ -1787,8 +2048,11 @@
       <c r="C33" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" s="8" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>36146</v>
       </c>
@@ -1799,7 +2063,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>36147</v>
       </c>
@@ -1809,8 +2073,11 @@
       <c r="C35" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" s="8" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>36148</v>
       </c>
@@ -1821,2809 +2088,2911 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36149</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36150</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>36151</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>36152</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>36153</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>36154</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>36156</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>36157</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>36158</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>36159</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>36160</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>36161</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>36162</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>36163</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>36164</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>36165</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>36166</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>36167</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>36168</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>36169</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>36170</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>36171</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>36172</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>36173</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>36174</v>
       </c>
       <c r="B61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>36175</v>
       </c>
       <c r="B62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C62" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>36176</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C63" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>36177</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C64" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>36178</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C65" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>36179</v>
       </c>
       <c r="B66" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C66" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>36180</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C67" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>36181</v>
       </c>
       <c r="B68" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C68" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>36182</v>
       </c>
       <c r="B69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C69" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>36183</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C70" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>36184</v>
       </c>
       <c r="B71" t="s">
+        <v>74</v>
+      </c>
+      <c r="C71" t="s">
         <v>75</v>
       </c>
-      <c r="C71" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" s="8" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>36185</v>
       </c>
       <c r="B72" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>36186</v>
       </c>
       <c r="B73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>36187</v>
       </c>
       <c r="B74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>36188</v>
       </c>
       <c r="B75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>36190</v>
       </c>
       <c r="B76" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>36191</v>
       </c>
       <c r="B77" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>36192</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>36193</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>36194</v>
       </c>
       <c r="B80" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>36195</v>
       </c>
       <c r="B81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>36196</v>
       </c>
       <c r="B82" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>36197</v>
       </c>
       <c r="B83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>36198</v>
       </c>
       <c r="B84" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>36199</v>
       </c>
       <c r="B85" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>36200</v>
       </c>
       <c r="B86" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>36201</v>
       </c>
       <c r="B87" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>36202</v>
       </c>
       <c r="B88" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>36203</v>
       </c>
       <c r="B89" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>36204</v>
       </c>
       <c r="B90" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>36205</v>
       </c>
       <c r="B91" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>36206</v>
       </c>
       <c r="B92" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>36207</v>
       </c>
       <c r="B93" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>36208</v>
       </c>
       <c r="B94" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>36209</v>
       </c>
       <c r="B95" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>36210</v>
       </c>
       <c r="B96" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>36211</v>
       </c>
       <c r="B97" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>36212</v>
       </c>
       <c r="B98" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>36213</v>
       </c>
       <c r="B99" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>36214</v>
       </c>
       <c r="B100" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>36215</v>
       </c>
       <c r="B101" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>36216</v>
       </c>
       <c r="B102" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>36217</v>
       </c>
       <c r="B103" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>36218</v>
       </c>
       <c r="B104" t="s">
+        <v>108</v>
+      </c>
+      <c r="C104" t="s">
         <v>109</v>
       </c>
-      <c r="C104" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>35356</v>
       </c>
       <c r="B105" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C105" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>35357</v>
       </c>
       <c r="B106" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C106" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>35358</v>
       </c>
       <c r="B107" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C107" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>35359</v>
       </c>
       <c r="B108" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C108" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>35360</v>
       </c>
       <c r="B109" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C109" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>35361</v>
       </c>
       <c r="B110" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C110" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>35362</v>
       </c>
       <c r="B111" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C111" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>35363</v>
       </c>
       <c r="B112" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C112" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>35364</v>
       </c>
       <c r="B113" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C113" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>35365</v>
       </c>
       <c r="B114" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C114" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>35366</v>
       </c>
       <c r="B115" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C115" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>35367</v>
       </c>
       <c r="B116" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C116" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>35368</v>
       </c>
       <c r="B117" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C117" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>35369</v>
       </c>
       <c r="B118" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C118" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>35370</v>
       </c>
       <c r="B119" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C119" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>35371</v>
       </c>
       <c r="B120" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C120" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>35372</v>
       </c>
       <c r="B121" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C121" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>35373</v>
       </c>
       <c r="B122" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C122" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>35374</v>
       </c>
       <c r="B123" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C123" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>35375</v>
       </c>
       <c r="B124" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C124" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>35376</v>
       </c>
       <c r="B125" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C125" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>35377</v>
       </c>
       <c r="B126" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C126" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>35378</v>
       </c>
       <c r="B127" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C127" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>35379</v>
       </c>
       <c r="B128" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C128" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>35380</v>
       </c>
       <c r="B129" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C129" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>35381</v>
       </c>
       <c r="B130" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C130" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>35382</v>
       </c>
       <c r="B131" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C131" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>35383</v>
       </c>
       <c r="B132" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C132" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>35384</v>
       </c>
       <c r="B133" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C133" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>35385</v>
       </c>
       <c r="B134" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C134" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>35386</v>
       </c>
       <c r="B135" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C135" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>35387</v>
       </c>
       <c r="B136" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C136" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>35388</v>
       </c>
       <c r="B137" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C137" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>35389</v>
       </c>
       <c r="B138" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C138" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>35390</v>
       </c>
       <c r="B139" t="s">
+        <v>144</v>
+      </c>
+      <c r="C139" t="s">
         <v>145</v>
       </c>
-      <c r="C139" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>35391</v>
       </c>
       <c r="B140" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C140" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>35392</v>
       </c>
       <c r="B141" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C141" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>35393</v>
       </c>
       <c r="B142" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C142" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>35394</v>
       </c>
       <c r="B143" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C143" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>35395</v>
       </c>
       <c r="B144" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C144" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>35396</v>
       </c>
       <c r="B145" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C145" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>35397</v>
       </c>
       <c r="B146" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C146" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>35399</v>
       </c>
       <c r="B147" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C147" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>35400</v>
       </c>
       <c r="B148" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C148" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>35401</v>
       </c>
       <c r="B149" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C149" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>35402</v>
       </c>
       <c r="B150" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C150" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>35403</v>
       </c>
       <c r="B151" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C151" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>35404</v>
       </c>
       <c r="B152" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C152" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>35405</v>
       </c>
       <c r="B153" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C153" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>35406</v>
       </c>
       <c r="B154" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C154" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>35407</v>
       </c>
       <c r="B155" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C155" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>35408</v>
       </c>
       <c r="B156" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C156" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>35409</v>
       </c>
       <c r="B157" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C157" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>35410</v>
       </c>
       <c r="B158" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C158" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>35411</v>
       </c>
       <c r="B159" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C159" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>35412</v>
       </c>
       <c r="B160" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C160" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>35413</v>
       </c>
       <c r="B161" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C161" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>35414</v>
       </c>
       <c r="B162" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C162" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>35416</v>
       </c>
       <c r="B163" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C163" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>35417</v>
       </c>
       <c r="B164" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C164" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>35418</v>
       </c>
       <c r="B165" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C165" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>35419</v>
       </c>
       <c r="B166" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C166" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>35420</v>
       </c>
       <c r="B167" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C167" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>35421</v>
       </c>
       <c r="B168" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C168" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>35422</v>
       </c>
       <c r="B169" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C169" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>35423</v>
       </c>
       <c r="B170" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C170" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>35424</v>
       </c>
       <c r="B171" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C171" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>35425</v>
       </c>
       <c r="B172" t="s">
+        <v>178</v>
+      </c>
+      <c r="C172" t="s">
         <v>179</v>
       </c>
-      <c r="C172" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>35426</v>
       </c>
       <c r="B173" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C173" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>35427</v>
       </c>
       <c r="B174" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C174" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>35428</v>
       </c>
       <c r="B175" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C175" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>35429</v>
       </c>
       <c r="B176" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C176" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>35430</v>
       </c>
       <c r="B177" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C177" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>35431</v>
       </c>
       <c r="B178" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C178" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>35432</v>
       </c>
       <c r="B179" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C179" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>35433</v>
       </c>
       <c r="B180" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C180" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>35434</v>
       </c>
       <c r="B181" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C181" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>35436</v>
       </c>
       <c r="B182" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C182" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>35437</v>
       </c>
       <c r="B183" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C183" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>35438</v>
       </c>
       <c r="B184" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C184" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>35439</v>
       </c>
       <c r="B185" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C185" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>35440</v>
       </c>
       <c r="B186" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C186" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>35441</v>
       </c>
       <c r="B187" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C187" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>35442</v>
       </c>
       <c r="B188" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C188" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>35443</v>
       </c>
       <c r="B189" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C189" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>35444</v>
       </c>
       <c r="B190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C190" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>35446</v>
       </c>
       <c r="B191" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C191" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>35447</v>
       </c>
       <c r="B192" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C192" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>35448</v>
       </c>
       <c r="B193" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C193" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>35449</v>
       </c>
       <c r="B194" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C194" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>35450</v>
       </c>
       <c r="B195" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C195" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>35451</v>
       </c>
       <c r="B196" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C196" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>35452</v>
       </c>
       <c r="B197" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C197" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>35453</v>
       </c>
       <c r="B198" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C198" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>35454</v>
       </c>
       <c r="B199" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C199" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>35455</v>
       </c>
       <c r="B200" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C200" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>35456</v>
       </c>
       <c r="B201" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C201" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>35458</v>
       </c>
       <c r="B202" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C202" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>35459</v>
       </c>
       <c r="B203" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C203" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>35460</v>
       </c>
       <c r="B204" t="s">
+        <v>211</v>
+      </c>
+      <c r="C204" t="s">
         <v>212</v>
       </c>
-      <c r="C204" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="205" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>34545</v>
       </c>
       <c r="B205" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C205" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>34547</v>
       </c>
       <c r="B206" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C206" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>34615</v>
       </c>
       <c r="B207" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C207" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>34548</v>
       </c>
       <c r="B208" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C208" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>34549</v>
       </c>
       <c r="B209" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C209" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>34551</v>
       </c>
       <c r="B210" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C210" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>34552</v>
       </c>
       <c r="B211" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C211" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>34616</v>
       </c>
       <c r="B212" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C212" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>34625</v>
       </c>
       <c r="B213" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C213" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>34553</v>
       </c>
       <c r="B214" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C214" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>34554</v>
       </c>
       <c r="B215" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C215" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>34629</v>
       </c>
       <c r="B216" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C216" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>34630</v>
       </c>
       <c r="B217" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C217" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>34556</v>
       </c>
       <c r="B218" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C218" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>34631</v>
       </c>
       <c r="B219" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C219" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>34633</v>
       </c>
       <c r="B220" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C220" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>34636</v>
       </c>
       <c r="B221" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C221" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>34560</v>
       </c>
       <c r="B222" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C222" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>34561</v>
       </c>
       <c r="B223" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C223" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>34562</v>
       </c>
       <c r="B224" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C224" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>34565</v>
       </c>
       <c r="B225" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C225" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>34567</v>
       </c>
       <c r="B226" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C226" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>34569</v>
       </c>
       <c r="B227" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C227" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>34570</v>
       </c>
       <c r="B228" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C228" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>34571</v>
       </c>
       <c r="B229" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C229" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>34572</v>
       </c>
       <c r="B230" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C230" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>34645</v>
       </c>
       <c r="B231" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C231" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>34647</v>
       </c>
       <c r="B232" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C232" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>34575</v>
       </c>
       <c r="B233" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C233" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>34576</v>
       </c>
       <c r="B234" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C234" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>34580</v>
       </c>
       <c r="B235" t="s">
+        <v>242</v>
+      </c>
+      <c r="C235" t="s">
         <v>243</v>
       </c>
-      <c r="C235" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="236" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>34582</v>
       </c>
       <c r="B236" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C236" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>34583</v>
       </c>
       <c r="B237" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C237" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>34618</v>
       </c>
       <c r="B238" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C238" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>34584</v>
       </c>
       <c r="B239" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C239" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>34619</v>
       </c>
       <c r="B240" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C240" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>34620</v>
       </c>
       <c r="B241" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C241" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>34586</v>
       </c>
       <c r="B242" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C242" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>34589</v>
       </c>
       <c r="B243" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C243" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>34590</v>
       </c>
       <c r="B244" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C244" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>34623</v>
       </c>
       <c r="B245" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C245" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>34593</v>
       </c>
       <c r="B246" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C246" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>34597</v>
       </c>
       <c r="B247" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C247" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>34598</v>
       </c>
       <c r="B248" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C248" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>34637</v>
       </c>
       <c r="B249" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C249" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>34599</v>
       </c>
       <c r="B250" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C250" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>34600</v>
       </c>
       <c r="B251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>34639</v>
       </c>
       <c r="B252" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>34640</v>
       </c>
       <c r="B253" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C253" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>34601</v>
       </c>
       <c r="B254" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C254" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>34602</v>
       </c>
       <c r="B255" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C255" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>34603</v>
       </c>
       <c r="B256" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C256" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>34604</v>
       </c>
       <c r="B257" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C257" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>34642</v>
       </c>
       <c r="B258" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C258" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>34608</v>
       </c>
       <c r="B259" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C259" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>34609</v>
       </c>
       <c r="B260" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C260" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>34610</v>
       </c>
       <c r="B261" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C261" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>34612</v>
       </c>
       <c r="B262" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C262" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>34644</v>
       </c>
       <c r="B263" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C263" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>34648</v>
       </c>
       <c r="B264" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C264" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>34613</v>
       </c>
       <c r="B265" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C265" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>34649</v>
       </c>
       <c r="B266" t="s">
+        <v>274</v>
+      </c>
+      <c r="C266" t="s">
         <v>275</v>
       </c>
-      <c r="C266" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="267" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>34581</v>
       </c>
       <c r="B267" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C267" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>34550</v>
       </c>
       <c r="B268" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C268" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>34617</v>
       </c>
       <c r="B269" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C269" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>34585</v>
       </c>
       <c r="B270" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C270" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>34587</v>
       </c>
       <c r="B271" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C271" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>34624</v>
       </c>
       <c r="B272" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C272" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>34555</v>
       </c>
       <c r="B273" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C273" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>34627</v>
       </c>
       <c r="B274" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C274" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>34628</v>
       </c>
       <c r="B275" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C275" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>34591</v>
       </c>
       <c r="B276" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C276" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>34592</v>
       </c>
       <c r="B277" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C277" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>34594</v>
       </c>
       <c r="B278" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C278" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>34595</v>
       </c>
       <c r="B279" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C279" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>34638</v>
       </c>
       <c r="B280" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C280" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>34634</v>
       </c>
       <c r="B281" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C281" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>34563</v>
       </c>
       <c r="B282" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C282" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>34566</v>
       </c>
       <c r="B283" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C283" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>34606</v>
       </c>
       <c r="B284" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C284" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>34607</v>
       </c>
       <c r="B285" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C285" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>34611</v>
       </c>
       <c r="B286" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C286" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>34646</v>
       </c>
       <c r="B287" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C287" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>34574</v>
       </c>
       <c r="B288" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C288" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>34614</v>
       </c>
       <c r="B289" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C289" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>34577</v>
       </c>
       <c r="B290" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C290" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>34578</v>
       </c>
       <c r="B291" t="s">
+        <v>299</v>
+      </c>
+      <c r="C291" t="s">
         <v>300</v>
-      </c>
-      <c r="C291" t="s">
-        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -4631,6 +5000,6 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>